--- a/frotas_abastecimentos.xlsx
+++ b/frotas_abastecimentos.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:L1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -487,190 +487,6 @@
       <c r="L1" s="1" t="inlineStr">
         <is>
           <t>nota_anexo</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>SIN4I57</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>50</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Etanol</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>48.97</v>
-      </c>
-      <c r="F2" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="G2" t="n">
-        <v>192.9418</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Empaza</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>SIN4I57</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>55787</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Etanol</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>30</v>
-      </c>
-      <c r="F3" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="G3" t="n">
-        <v>111</v>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Auto Posto Sorrisao</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Eurider</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>05/05/2026 13:26</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>SIN4I57</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>55787</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Etanol</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>30</v>
-      </c>
-      <c r="F4" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="G4" t="n">
-        <v>111</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Auto Posto Sorrisao</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Eurider</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>05/05/2026 13:26</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>SIN4I57</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>51258</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Etanol</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>40</v>
-      </c>
-      <c r="F5" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="G5" t="n">
-        <v>153.6</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Podto Nossa Senhora</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>VIAGEM PARA BOA ESPERANÇA</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Eurider</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>05/05/2026 14:21</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>C:\Users\Dell\Desktop\Alpes Gestão e Facilities\Anexos Frotas\20260505_142119_SIN4I57_abastecimento_desk.jpg</t>
         </is>
       </c>
     </row>

--- a/frotas_abastecimentos.xlsx
+++ b/frotas_abastecimentos.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:N1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,22 +471,32 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>responsavel_lancamento</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>registrado_em</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>nota_anexo</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>status_conferencia</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>observacao_administrativo</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>observacoes</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>responsavel_lancamento</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>registrado_em</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>nota_anexo</t>
         </is>
       </c>
     </row>
